--- a/Dieta.xlsx
+++ b/Dieta.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0c3092358fa2c973/Área de Trabalho/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuário\GIT\rotina-dieta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="8_{ABBA6873-34F6-42F8-8C9A-A91AA5E589B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B23AAA0-390D-46F9-96CD-CE2F5A3F11DA}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59D9DBED-78BB-4EB1-A957-00313B9EE634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,13 +16,14 @@
     <sheet name="Calculadora" sheetId="1" r:id="rId1"/>
     <sheet name="Referências" sheetId="2" r:id="rId2"/>
     <sheet name="Dieta" sheetId="3" r:id="rId3"/>
+    <sheet name="Rotina" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="232">
   <si>
     <t>Calculadora de Calorias e Macros para Ganho de Massa</t>
   </si>
@@ -54,7 +55,7 @@
     <t>Nível de atividade</t>
   </si>
   <si>
-    <t>Moderado (3–5x/semana)</t>
+    <t>Intenso (6–7x/semana)</t>
   </si>
   <si>
     <t>Superávit desejado (kcal)</t>
@@ -168,15 +169,15 @@
     <t>0,7–1,0 g/kg/dia</t>
   </si>
   <si>
+    <t>Moderado (3–5x/semana)</t>
+  </si>
+  <si>
     <t>Superávit inicial</t>
   </si>
   <si>
     <t>+200 a +300 kcal/dia</t>
   </si>
   <si>
-    <t>Intenso (6–7x/semana)</t>
-  </si>
-  <si>
     <t>Muito intenso / trabalho físico</t>
   </si>
   <si>
@@ -306,227 +307,525 @@
     <t>~150 g</t>
   </si>
   <si>
+    <t>Após 23/10</t>
+  </si>
+  <si>
+    <t>em casa</t>
+  </si>
+  <si>
+    <t>Atividades físicas</t>
+  </si>
+  <si>
+    <t>rotina</t>
+  </si>
+  <si>
+    <t>segunda-feira</t>
+  </si>
+  <si>
+    <t>terça-feira</t>
+  </si>
+  <si>
+    <t>quarta-feira</t>
+  </si>
+  <si>
+    <t>Kung Fu</t>
+  </si>
+  <si>
+    <t>Francês</t>
+  </si>
+  <si>
+    <t>Samba Rock</t>
+  </si>
+  <si>
+    <t>Tech</t>
+  </si>
+  <si>
+    <t>Academia</t>
+  </si>
+  <si>
+    <t>Inglês</t>
+  </si>
+  <si>
+    <t>Trabalho</t>
+  </si>
+  <si>
+    <t>Almoço/Academia</t>
+  </si>
+  <si>
+    <t>Alimentação e Banho</t>
+  </si>
+  <si>
+    <t>Cavaquinho</t>
+  </si>
+  <si>
+    <t>App de Bares</t>
+  </si>
+  <si>
+    <t>Livro</t>
+  </si>
+  <si>
+    <t>Sem horário</t>
+  </si>
+  <si>
+    <t>Alongamento</t>
+  </si>
+  <si>
+    <t>Memorizaton Hack</t>
+  </si>
+  <si>
+    <t>Trabalho presencial</t>
+  </si>
+  <si>
+    <t>quinta-feita</t>
+  </si>
+  <si>
+    <t>sexta-feira</t>
+  </si>
+  <si>
+    <t>Almoço</t>
+  </si>
+  <si>
+    <t>Ir para casa</t>
+  </si>
+  <si>
     <t>Dia</t>
   </si>
   <si>
+    <t>Horário</t>
+  </si>
+  <si>
+    <t>Comida simples</t>
+  </si>
+  <si>
+    <t>Quantidades</t>
+  </si>
+  <si>
+    <t>PLANO NUTRICIONAL</t>
+  </si>
+  <si>
     <t>Segunda</t>
   </si>
   <si>
+    <t>7h15</t>
+  </si>
+  <si>
+    <t>Café da manhã</t>
+  </si>
+  <si>
+    <t>Pão + queijo + leite + aveia + banana</t>
+  </si>
+  <si>
+    <t>Pão|3 fatias
+Queijo muçarela/prato|30 g
+Leite|250 ml
+Aveia|70 g
+Banana|1 média</t>
+  </si>
+  <si>
+    <t>Meta calórica</t>
+  </si>
+  <si>
+    <t>~3.494 kcal/dia</t>
+  </si>
+  <si>
+    <t>10h30</t>
+  </si>
+  <si>
+    <t>Lanche</t>
+  </si>
+  <si>
+    <t>Whey + mamão</t>
+  </si>
+  <si>
+    <t>Whey|30 g
+Mamão|200 g</t>
+  </si>
+  <si>
+    <t>~166 g/dia</t>
+  </si>
+  <si>
+    <t>13h00</t>
+  </si>
+  <si>
+    <t>Arroz + feijão + frango + legumes + abacate</t>
+  </si>
+  <si>
+    <t>Arroz cozido|350 g
+Feijão cozido|150 g
+Frango|120 g
+Legumes/salada|200 g
+Abacate|100 g</t>
+  </si>
+  <si>
+    <t>~75 g/dia</t>
+  </si>
+  <si>
+    <t>16h30</t>
+  </si>
+  <si>
+    <t>Pão + queijo + uva</t>
+  </si>
+  <si>
+    <t>Pão|2 fatias
+Queijo|30 g
+Uva|100 g</t>
+  </si>
+  <si>
+    <t>Ovo</t>
+  </si>
+  <si>
+    <t>2 refeições/semana</t>
+  </si>
+  <si>
+    <t>17h45</t>
+  </si>
+  <si>
+    <t>Pré-Kung Fu</t>
+  </si>
+  <si>
+    <t>Banana + pão</t>
+  </si>
+  <si>
+    <t>Banana|1 média
+Pão|2 fatias</t>
+  </si>
+  <si>
+    <t>Plano principal</t>
+  </si>
+  <si>
+    <t>19h00–21h00</t>
+  </si>
+  <si>
+    <t>🥋 Kung Fu</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>21h15</t>
+  </si>
+  <si>
+    <t>Jantar / pós</t>
+  </si>
+  <si>
+    <t>Arroz + feijão + carne + batata + legumes</t>
+  </si>
+  <si>
+    <t>Arroz cozido|300 g
+Feijão|100 g
+Carne bovina magra|120 g
+Batata cozida/assada|100 g
+Legumes/salada|200 g</t>
+  </si>
+  <si>
+    <t>22h30</t>
+  </si>
+  <si>
+    <t>Ceia</t>
+  </si>
+  <si>
+    <t>Leite + manga</t>
+  </si>
+  <si>
+    <t>Leite|250 ml
+Manga|150 g</t>
+  </si>
+  <si>
     <t>Terça</t>
   </si>
   <si>
+    <t>Pão + ovos + leite + aveia + banana</t>
+  </si>
+  <si>
+    <t>Pão|3 fatias
+Ovos|2 unidades
+Leite|250 ml
+Aveia|60 g
+Banana|1 média</t>
+  </si>
+  <si>
+    <t>10h15</t>
+  </si>
+  <si>
+    <t>11h20</t>
+  </si>
+  <si>
+    <t>Pré-academia</t>
+  </si>
+  <si>
+    <t>Pão + banana</t>
+  </si>
+  <si>
+    <t>Pão|2 fatias
+Banana|1 média</t>
+  </si>
+  <si>
+    <t>12h00–13h00</t>
+  </si>
+  <si>
+    <t>🏋️ Academia</t>
+  </si>
+  <si>
+    <t>13h10</t>
+  </si>
+  <si>
+    <t>Almoço / pós</t>
+  </si>
+  <si>
+    <t>Arroz cozido|350 g
+Feijão cozido|150 g
+Frango|120 g
+Legumes/salada|200 g
+Abacate|80 g</t>
+  </si>
+  <si>
+    <t>Pré-Samba</t>
+  </si>
+  <si>
+    <t>Pão|2 fatias
+Queijo|30 g
+Uva|120 g</t>
+  </si>
+  <si>
+    <t>18h00–20h00</t>
+  </si>
+  <si>
+    <t>🕺 Samba Rock</t>
+  </si>
+  <si>
+    <t>20h15</t>
+  </si>
+  <si>
+    <t>Arroz cozido|300 g
+Feijão|100 g
+Carne bovina magra|120 g
+Batata|100 g
+Legumes/salada|200 g</t>
+  </si>
+  <si>
+    <t>22h15</t>
+  </si>
+  <si>
     <t>Quarta</t>
   </si>
   <si>
+    <t>Pão|3 fatias
+Queijo|30 g
+Leite|250 ml
+Aveia|70 g
+Banana|1 média</t>
+  </si>
+  <si>
+    <t>Arroz + feijão + carne + legumes + abacate</t>
+  </si>
+  <si>
+    <t>Arroz cozido|350 g
+Feijão|150 g
+Carne bovina magra|120 g
+Legumes/salada|200 g
+Abacate|100 g</t>
+  </si>
+  <si>
+    <t>Arroz + feijão + frango + batata + legumes</t>
+  </si>
+  <si>
+    <t>Arroz cozido|300 g
+Feijão|100 g
+Frango|120 g
+Batata|100 g
+Legumes/salada|200 g</t>
+  </si>
+  <si>
+    <t>Quinta — presencial</t>
+  </si>
+  <si>
+    <t>Marmita</t>
+  </si>
+  <si>
+    <t>Arroz cozido|350 g
+Feijão|150 g
+Frango|120 g
+Legumes|200 g
+Abacate|80 g</t>
+  </si>
+  <si>
+    <t>Lanche no trabalho</t>
+  </si>
+  <si>
+    <t>Pão + queijo + fruta</t>
+  </si>
+  <si>
+    <t>Pão|2 fatias
+Queijo|30 g
+Banana|1 média</t>
+  </si>
+  <si>
+    <t>19h15</t>
+  </si>
+  <si>
+    <t>Lanche ao chegar / caminho</t>
+  </si>
+  <si>
+    <t>Whey + aveia + leite</t>
+  </si>
+  <si>
+    <t>Whey|30 g
+Aveia|40 g
+Leite|250 ml</t>
+  </si>
+  <si>
+    <t>20h30</t>
+  </si>
+  <si>
+    <t>Jantar</t>
+  </si>
+  <si>
+    <t>Manga ou mamão</t>
+  </si>
+  <si>
+    <t>Manga|150 g
+OU mamão|200 g</t>
+  </si>
+  <si>
+    <t>Sexta — presencial</t>
+  </si>
+  <si>
+    <t>Arroz cozido|350 g
+Feijão|150 g
+Carne bovina magra|120 g
+Legumes|200 g
+Abacate|80 g</t>
+  </si>
+  <si>
+    <t>16h15</t>
+  </si>
+  <si>
+    <t>17h30</t>
+  </si>
+  <si>
     <t>Sábado</t>
   </si>
   <si>
+    <t>6h50</t>
+  </si>
+  <si>
+    <t>8h00–9h00</t>
+  </si>
+  <si>
+    <t>9h20</t>
+  </si>
+  <si>
+    <t>Café / pós</t>
+  </si>
+  <si>
+    <t>Pão + ovos + leite + aveia + mamão + whey</t>
+  </si>
+  <si>
+    <t>Pão|3 fatias
+Ovos|2 unidades
+Leite|250 ml
+Aveia|60 g
+Mamão|200 g
+Whey|30 g</t>
+  </si>
+  <si>
+    <t>Arroz cozido|350 g
+Feijão|150 g
+Frango|120 g
+Legumes/salada|200 g
+Abacate|100 g</t>
+  </si>
+  <si>
+    <t>Pão + queijo + banana + uva</t>
+  </si>
+  <si>
+    <t>Pão|2 fatias
+Queijo|30 g
+Banana|1 média
+Uva|100 g</t>
+  </si>
+  <si>
+    <t>20h00</t>
+  </si>
+  <si>
     <t>Domingo</t>
   </si>
   <si>
-    <t>Horário</t>
-  </si>
-  <si>
-    <t>Comida simples</t>
-  </si>
-  <si>
-    <t>7h–8h</t>
-  </si>
-  <si>
-    <t>Café</t>
-  </si>
-  <si>
-    <t>Pão + queijo + leite + aveia + banana</t>
-  </si>
-  <si>
-    <t>10h–11h</t>
-  </si>
-  <si>
-    <t>Lanche</t>
-  </si>
-  <si>
-    <t>Whey + mamão</t>
-  </si>
-  <si>
-    <t>12h–13h</t>
-  </si>
-  <si>
-    <t>Almoço</t>
-  </si>
-  <si>
-    <t>Arroz + feijão + frango/carne + legumes/salada</t>
-  </si>
-  <si>
-    <t>17h30–18h</t>
-  </si>
-  <si>
-    <t>Pré-Kung Fu</t>
-  </si>
-  <si>
-    <t>Pão + queijo + banana + uva</t>
-  </si>
-  <si>
-    <t>19h30–21h</t>
-  </si>
-  <si>
-    <t>🥋 Kung Fu</t>
-  </si>
-  <si>
-    <t>—</t>
-  </si>
-  <si>
-    <t>21h30</t>
-  </si>
-  <si>
-    <t>Jantar / pós</t>
-  </si>
-  <si>
-    <t>Arroz + feijão + frango/carne + legumes</t>
-  </si>
-  <si>
-    <t>10h30–11h</t>
-  </si>
-  <si>
-    <t>Pré-academia</t>
-  </si>
-  <si>
-    <t>Banana ou pão + queijo</t>
-  </si>
-  <si>
-    <t>🏋️ Academia</t>
-  </si>
-  <si>
-    <t>13h15</t>
-  </si>
-  <si>
-    <t>Almoço / pós</t>
-  </si>
-  <si>
-    <t>16h30–17h</t>
-  </si>
-  <si>
-    <t>Pré-Samba</t>
-  </si>
-  <si>
-    <t>Pão + queijo + banana ou uva</t>
-  </si>
-  <si>
-    <t>18h–20h</t>
-  </si>
-  <si>
-    <t>🕺 Samba Rock</t>
-  </si>
-  <si>
-    <t>20h30</t>
-  </si>
-  <si>
-    <t>Arroz + feijão + frango/carne + batata + legumes</t>
-  </si>
-  <si>
-    <t>Quinta — presencial</t>
-  </si>
-  <si>
-    <t>Pão + queijo + leite + aveia + fruta</t>
-  </si>
-  <si>
-    <t>Whey + fruta</t>
-  </si>
-  <si>
-    <t>Marmita</t>
-  </si>
-  <si>
-    <t>Arroz + feijão + frango + brócolis/couve-flor</t>
-  </si>
-  <si>
-    <t>16h–17h</t>
-  </si>
-  <si>
-    <t>Whey + banana/mamão</t>
-  </si>
-  <si>
-    <t>19h–19h30</t>
-  </si>
-  <si>
-    <t>Pão + queijo + banana</t>
-  </si>
-  <si>
-    <t>21h</t>
-  </si>
-  <si>
-    <t>22h15–22h30</t>
-  </si>
-  <si>
-    <t>Sexta — presencial</t>
-  </si>
-  <si>
-    <t>15h30–16h</t>
-  </si>
-  <si>
-    <t>7h</t>
-  </si>
-  <si>
-    <t>Banana + 1–2 fatias de pão</t>
-  </si>
-  <si>
-    <t>8h</t>
-  </si>
-  <si>
-    <t>9h30</t>
-  </si>
-  <si>
-    <t>Café / pós</t>
-  </si>
-  <si>
-    <t>Pão + queijo + leite + aveia + fruta + whey</t>
-  </si>
-  <si>
-    <t>12h30–13h30</t>
-  </si>
-  <si>
-    <t>Arroz + feijão + carne/frango + legumes</t>
-  </si>
-  <si>
-    <t>Fruta + pão/queijo ou whey</t>
-  </si>
-  <si>
-    <t>20h</t>
-  </si>
-  <si>
-    <t>Jantar</t>
-  </si>
-  <si>
-    <t>Arroz/batata + frango/carne + legumes</t>
-  </si>
-  <si>
-    <t>Pão + queijo + leite + aveia + banana/mamão</t>
-  </si>
-  <si>
-    <t>10h</t>
-  </si>
-  <si>
-    <t>Banana, uva ou pão</t>
-  </si>
-  <si>
-    <t>11h</t>
+    <t>8h00</t>
+  </si>
+  <si>
+    <t>9h50</t>
+  </si>
+  <si>
+    <t>Pão + uva</t>
+  </si>
+  <si>
+    <t>Pão|2 fatias
+Uva|100 g</t>
+  </si>
+  <si>
+    <t>11h00–12h00</t>
   </si>
   <si>
     <t>12h30</t>
   </si>
   <si>
-    <t>Arroz + feijão + carne/frango + batata + legumes</t>
+    <t>Arroz + feijão + carne + batata + legumes + abacate</t>
+  </si>
+  <si>
+    <t>Arroz cozido|350 g
+Feijão|150 g
+Carne bovina magra|120 g
+Batata|100 g
+Legumes/salada|200 g
+Abacate|80 g</t>
+  </si>
+  <si>
+    <t>Whey + mamão + pão</t>
+  </si>
+  <si>
+    <t>Whey|30 g
+Mamão|200 g
+Pão|2 fatias</t>
+  </si>
+  <si>
+    <t>Arroz + feijão + frango + legumes</t>
+  </si>
+  <si>
+    <t>Arroz cozido|300 g
+Feijão|100 g
+Frango|120 g
+Legumes/salada|200 g</t>
+  </si>
+  <si>
+    <t>Almoço/Inglês</t>
+  </si>
+  <si>
+    <t>Almoço/Francês</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="h:mm;@"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
@@ -566,16 +865,17 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Carlito"/>
-      <family val="2"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
+      <color rgb="FF4C1D95"/>
       <name val="Carlito"/>
-      <family val="2"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -632,8 +932,23 @@
         <fgColor rgb="FFC6E0B4"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF70AD47"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDE9FE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="20">
+  <borders count="46">
     <border>
       <left/>
       <right/>
@@ -838,22 +1153,310 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9E1F2"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD9E1F2"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD9E1F2"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9E1F2"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD9E1F2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9E1F2"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9E1F2"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD9E1F2"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9E1F2"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9E1F2"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9E1F2"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD9E1F2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD9E1F2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD9E1F2"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD9E1F2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -865,34 +1468,34 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
@@ -901,125 +1504,260 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1242,13 +1980,13 @@
     <col min="4" max="4" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="24" t="s">
+    <row r="1" spans="1:4" ht="15.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="86" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
+      <c r="B1" s="86"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
@@ -1257,12 +1995,12 @@
       <c r="D2" s="2"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="87" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25"/>
+      <c r="B3" s="87"/>
+      <c r="C3" s="87"/>
+      <c r="D3" s="87"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
@@ -1325,7 +2063,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="9"/>
@@ -1507,38 +2245,38 @@
       <c r="D24" s="2"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="26" t="s">
+      <c r="A25" s="88" t="s">
         <v>36</v>
       </c>
-      <c r="B25" s="26"/>
-      <c r="C25" s="26"/>
-      <c r="D25" s="26"/>
+      <c r="B25" s="88"/>
+      <c r="C25" s="88"/>
+      <c r="D25" s="88"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="27" t="s">
+      <c r="A26" s="89" t="s">
         <v>37</v>
       </c>
-      <c r="B26" s="27"/>
-      <c r="C26" s="27"/>
-      <c r="D26" s="27"/>
+      <c r="B26" s="89"/>
+      <c r="C26" s="89"/>
+      <c r="D26" s="89"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="27"/>
-      <c r="B27" s="27"/>
-      <c r="C27" s="27"/>
-      <c r="D27" s="27"/>
+      <c r="A27" s="89"/>
+      <c r="B27" s="89"/>
+      <c r="C27" s="89"/>
+      <c r="D27" s="89"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="27"/>
-      <c r="B28" s="27"/>
-      <c r="C28" s="27"/>
-      <c r="D28" s="27"/>
+      <c r="A28" s="89"/>
+      <c r="B28" s="89"/>
+      <c r="C28" s="89"/>
+      <c r="D28" s="89"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="27"/>
-      <c r="B29" s="27"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="27"/>
+      <c r="A29" s="89"/>
+      <c r="B29" s="89"/>
+      <c r="C29" s="89"/>
+      <c r="D29" s="89"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="2"/>
@@ -1547,18 +2285,18 @@
       <c r="D30" s="2"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="28" t="s">
+      <c r="A31" s="90" t="s">
         <v>38</v>
       </c>
-      <c r="B31" s="28"/>
-      <c r="C31" s="28"/>
-      <c r="D31" s="28"/>
+      <c r="B31" s="90"/>
+      <c r="C31" s="90"/>
+      <c r="D31" s="90"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="28"/>
-      <c r="B32" s="28"/>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
+      <c r="A32" s="90"/>
+      <c r="B32" s="90"/>
+      <c r="C32" s="90"/>
+      <c r="D32" s="90"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1574,18 +2312,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0000-000001000000}">
-          <x14:formula1>
-            <xm:f>Referências!$A$2:$A$6</xm:f>
-          </x14:formula1>
-          <xm:sqref>B10</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
@@ -1647,22 +2373,22 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="B4" s="2">
         <v>1.55</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="B5" s="2">
         <v>1.7250000000000001</v>
@@ -1702,771 +2428,1063 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A520734C-E2AE-424D-B2AE-811C0D132D64}">
-  <dimension ref="A1:H46"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:L55"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.44140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.6640625" style="29" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.21875" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.21875" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="42.21875" style="29" bestFit="1" customWidth="1"/>
+    <col min="1" max="3" width="47.21875" style="24" customWidth="1"/>
+    <col min="4" max="4" width="47.21875" customWidth="1"/>
+    <col min="5" max="8" width="47.21875" style="24" customWidth="1"/>
+    <col min="9" max="9" width="47.21875" customWidth="1"/>
+    <col min="11" max="11" width="18" customWidth="1"/>
+    <col min="12" max="12" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="39" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A1" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="40" t="s">
+      <c r="B1" s="32" t="s">
         <v>52</v>
       </c>
-      <c r="C1" s="41" t="s">
+      <c r="C1" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="E1" s="57" t="s">
+      <c r="E1" s="64" t="s">
+        <v>120</v>
+      </c>
+      <c r="F1" s="65" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1" s="65" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1" s="66" t="s">
+        <v>122</v>
+      </c>
+      <c r="I1" s="67" t="s">
+        <v>123</v>
+      </c>
+      <c r="K1" s="91" t="s">
+        <v>124</v>
+      </c>
+      <c r="L1" s="91"/>
+    </row>
+    <row r="2" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+      <c r="A2" s="92" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="E2" s="95" t="s">
+        <v>125</v>
+      </c>
+      <c r="F2" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="G2" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="H2" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="I2" s="68" t="s">
+        <v>129</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="94"/>
+      <c r="B3" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="E3" s="96"/>
+      <c r="F3" s="27" t="s">
+        <v>132</v>
+      </c>
+      <c r="G3" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="H3" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="I3" s="68" t="s">
+        <v>135</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+      <c r="A4" s="94"/>
+      <c r="B4" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="E4" s="96"/>
+      <c r="F4" s="27" t="s">
+        <v>137</v>
+      </c>
+      <c r="G4" s="27" t="s">
+        <v>118</v>
+      </c>
+      <c r="H4" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="I4" s="68" t="s">
+        <v>139</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="94"/>
+      <c r="B5" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>62</v>
+      </c>
+      <c r="E5" s="96"/>
+      <c r="F5" s="58" t="s">
+        <v>141</v>
+      </c>
+      <c r="G5" s="58" t="s">
+        <v>133</v>
+      </c>
+      <c r="H5" s="59" t="s">
+        <v>142</v>
+      </c>
+      <c r="I5" s="68" t="s">
+        <v>143</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="93"/>
+      <c r="B6" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="E6" s="96"/>
+      <c r="F6" s="27" t="s">
+        <v>146</v>
+      </c>
+      <c r="G6" s="27" t="s">
+        <v>147</v>
+      </c>
+      <c r="H6" s="28" t="s">
+        <v>148</v>
+      </c>
+      <c r="I6" s="68" t="s">
+        <v>149</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="L6" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F1" s="58" t="s">
-        <v>99</v>
-      </c>
-      <c r="G1" s="58" t="s">
-        <v>51</v>
-      </c>
-      <c r="H1" s="59" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="30" t="s">
-        <v>54</v>
-      </c>
-      <c r="B2" s="31" t="s">
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" s="92" t="s">
+        <v>65</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="E7" s="99"/>
+      <c r="F7" s="75" t="s">
+        <v>151</v>
+      </c>
+      <c r="G7" s="78" t="s">
+        <v>152</v>
+      </c>
+      <c r="H7" s="76" t="s">
+        <v>153</v>
+      </c>
+      <c r="I7" s="77"/>
+    </row>
+    <row r="8" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+      <c r="A8" s="93"/>
+      <c r="B8" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="E8" s="95"/>
+      <c r="F8" s="25" t="s">
+        <v>154</v>
+      </c>
+      <c r="G8" s="25" t="s">
+        <v>155</v>
+      </c>
+      <c r="H8" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="I8" s="68" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="92" t="s">
+        <v>69</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="E9" s="96"/>
+      <c r="F9" s="58" t="s">
+        <v>158</v>
+      </c>
+      <c r="G9" s="58" t="s">
+        <v>159</v>
+      </c>
+      <c r="H9" s="59" t="s">
+        <v>160</v>
+      </c>
+      <c r="I9" s="68" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+      <c r="A10" s="94"/>
+      <c r="B10" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="E10" s="96" t="s">
+        <v>162</v>
+      </c>
+      <c r="F10" s="27" t="s">
+        <v>126</v>
+      </c>
+      <c r="G10" s="27" t="s">
+        <v>127</v>
+      </c>
+      <c r="H10" s="28" t="s">
+        <v>163</v>
+      </c>
+      <c r="I10" s="68" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="94"/>
+      <c r="B11" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="C11" s="28" t="s">
+        <v>75</v>
+      </c>
+      <c r="E11" s="96"/>
+      <c r="F11" s="58" t="s">
+        <v>165</v>
+      </c>
+      <c r="G11" s="58" t="s">
+        <v>133</v>
+      </c>
+      <c r="H11" s="59" t="s">
+        <v>134</v>
+      </c>
+      <c r="I11" s="68" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="94"/>
+      <c r="B12" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12" s="28" t="s">
+        <v>77</v>
+      </c>
+      <c r="E12" s="96"/>
+      <c r="F12" s="58" t="s">
+        <v>166</v>
+      </c>
+      <c r="G12" s="58" t="s">
+        <v>167</v>
+      </c>
+      <c r="H12" s="59" t="s">
+        <v>168</v>
+      </c>
+      <c r="I12" s="68" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" s="93"/>
+      <c r="B13" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="E13" s="97"/>
+      <c r="F13" s="79" t="s">
+        <v>170</v>
+      </c>
+      <c r="G13" s="81" t="s">
+        <v>171</v>
+      </c>
+      <c r="H13" s="80" t="s">
+        <v>153</v>
+      </c>
+      <c r="I13" s="77"/>
+    </row>
+    <row r="14" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+      <c r="A14" s="92" t="s">
+        <v>79</v>
+      </c>
+      <c r="B14" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="C2" s="32" t="s">
+      <c r="C14" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="E2" s="42" t="s">
-        <v>94</v>
-      </c>
-      <c r="F2" s="43" t="s">
-        <v>101</v>
-      </c>
-      <c r="G2" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="H2" s="44" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="33"/>
-      <c r="B3" s="34" t="s">
-        <v>57</v>
-      </c>
-      <c r="C3" s="35" t="s">
+      <c r="E14" s="98"/>
+      <c r="F14" s="60" t="s">
+        <v>172</v>
+      </c>
+      <c r="G14" s="60" t="s">
+        <v>173</v>
+      </c>
+      <c r="H14" s="61" t="s">
+        <v>138</v>
+      </c>
+      <c r="I14" s="68" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A15" s="94"/>
+      <c r="B15" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="C15" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="E3" s="45"/>
-      <c r="F3" s="46" t="s">
-        <v>104</v>
-      </c>
-      <c r="G3" s="46" t="s">
-        <v>105</v>
-      </c>
-      <c r="H3" s="47" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="33"/>
-      <c r="B4" s="34" t="s">
+      <c r="E15" s="95"/>
+      <c r="F15" s="25" t="s">
+        <v>141</v>
+      </c>
+      <c r="G15" s="25" t="s">
+        <v>175</v>
+      </c>
+      <c r="H15" s="26" t="s">
+        <v>142</v>
+      </c>
+      <c r="I15" s="68" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" s="94"/>
+      <c r="B16" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" s="28" t="s">
+        <v>64</v>
+      </c>
+      <c r="E16" s="97"/>
+      <c r="F16" s="79" t="s">
+        <v>177</v>
+      </c>
+      <c r="G16" s="81" t="s">
+        <v>178</v>
+      </c>
+      <c r="H16" s="80" t="s">
+        <v>153</v>
+      </c>
+      <c r="I16" s="77"/>
+    </row>
+    <row r="17" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+      <c r="A17" s="93"/>
+      <c r="B17" s="29" t="s">
+        <v>81</v>
+      </c>
+      <c r="C17" s="30" t="s">
+        <v>82</v>
+      </c>
+      <c r="E17" s="96"/>
+      <c r="F17" s="27" t="s">
+        <v>179</v>
+      </c>
+      <c r="G17" s="27" t="s">
+        <v>155</v>
+      </c>
+      <c r="H17" s="28" t="s">
+        <v>156</v>
+      </c>
+      <c r="I17" s="68" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="92" t="s">
+        <v>83</v>
+      </c>
+      <c r="B18" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="C18" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="E18" s="96"/>
+      <c r="F18" s="58" t="s">
+        <v>181</v>
+      </c>
+      <c r="G18" s="58" t="s">
+        <v>159</v>
+      </c>
+      <c r="H18" s="59" t="s">
+        <v>160</v>
+      </c>
+      <c r="I18" s="68" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+      <c r="A19" s="94"/>
+      <c r="B19" s="27" t="s">
+        <v>85</v>
+      </c>
+      <c r="C19" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="E19" s="96" t="s">
+        <v>182</v>
+      </c>
+      <c r="F19" s="27" t="s">
+        <v>126</v>
+      </c>
+      <c r="G19" s="27" t="s">
+        <v>127</v>
+      </c>
+      <c r="H19" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="I19" s="68" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="94"/>
+      <c r="B20" s="27" t="s">
+        <v>87</v>
+      </c>
+      <c r="C20" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="E20" s="98"/>
+      <c r="F20" s="60" t="s">
+        <v>132</v>
+      </c>
+      <c r="G20" s="60" t="s">
+        <v>133</v>
+      </c>
+      <c r="H20" s="61" t="s">
+        <v>134</v>
+      </c>
+      <c r="I20" s="68" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+      <c r="A21" s="94"/>
+      <c r="B21" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="C21" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="E21" s="95"/>
+      <c r="F21" s="25" t="s">
+        <v>137</v>
+      </c>
+      <c r="G21" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="H21" s="26" t="s">
+        <v>184</v>
+      </c>
+      <c r="I21" s="68" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A22" s="93"/>
+      <c r="B22" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="C22" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="E22" s="96"/>
+      <c r="F22" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="G22" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="H22" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="I22" s="68" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A23" s="92" t="s">
+        <v>90</v>
+      </c>
+      <c r="B23" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="C4" s="35" t="s">
+      <c r="C23" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="E4" s="45"/>
-      <c r="F4" s="46" t="s">
-        <v>107</v>
-      </c>
-      <c r="G4" s="46" t="s">
-        <v>108</v>
-      </c>
-      <c r="H4" s="47" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="33"/>
-      <c r="B5" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="C5" s="35" t="s">
-        <v>62</v>
-      </c>
-      <c r="E5" s="45"/>
-      <c r="F5" s="48" t="s">
-        <v>110</v>
-      </c>
-      <c r="G5" s="48" t="s">
-        <v>111</v>
-      </c>
-      <c r="H5" s="49" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="36"/>
-      <c r="B6" s="37" t="s">
-        <v>63</v>
-      </c>
-      <c r="C6" s="38" t="s">
-        <v>64</v>
-      </c>
-      <c r="E6" s="45"/>
-      <c r="F6" s="46" t="s">
-        <v>113</v>
-      </c>
-      <c r="G6" s="46" t="s">
-        <v>114</v>
-      </c>
-      <c r="H6" s="47" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="30" t="s">
-        <v>65</v>
-      </c>
-      <c r="B7" s="31" t="s">
-        <v>66</v>
-      </c>
-      <c r="C7" s="32" t="s">
-        <v>58</v>
-      </c>
-      <c r="E7" s="50"/>
-      <c r="F7" s="51" t="s">
-        <v>116</v>
-      </c>
-      <c r="G7" s="51" t="s">
-        <v>117</v>
-      </c>
-      <c r="H7" s="52" t="s">
+      <c r="E23" s="96"/>
+      <c r="F23" s="27" t="s">
+        <v>146</v>
+      </c>
+      <c r="G23" s="27" t="s">
+        <v>147</v>
+      </c>
+      <c r="H23" s="28" t="s">
+        <v>148</v>
+      </c>
+      <c r="I23" s="68" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" s="93"/>
+      <c r="B24" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="C24" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="E24" s="97"/>
+      <c r="F24" s="79" t="s">
+        <v>151</v>
+      </c>
+      <c r="G24" s="81" t="s">
+        <v>152</v>
+      </c>
+      <c r="H24" s="80" t="s">
+        <v>153</v>
+      </c>
+      <c r="I24" s="77"/>
+    </row>
+    <row r="25" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+      <c r="E25" s="96"/>
+      <c r="F25" s="58" t="s">
+        <v>154</v>
+      </c>
+      <c r="G25" s="58" t="s">
+        <v>155</v>
+      </c>
+      <c r="H25" s="59" t="s">
+        <v>186</v>
+      </c>
+      <c r="I25" s="68" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="E26" s="96"/>
+      <c r="F26" s="27" t="s">
+        <v>158</v>
+      </c>
+      <c r="G26" s="27" t="s">
+        <v>159</v>
+      </c>
+      <c r="H26" s="28" t="s">
+        <v>160</v>
+      </c>
+      <c r="I26" s="68" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+      <c r="E27" s="98" t="s">
+        <v>188</v>
+      </c>
+      <c r="F27" s="60" t="s">
+        <v>126</v>
+      </c>
+      <c r="G27" s="60" t="s">
+        <v>127</v>
+      </c>
+      <c r="H27" s="61" t="s">
+        <v>128</v>
+      </c>
+      <c r="I27" s="68" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="E28" s="95"/>
+      <c r="F28" s="25" t="s">
+        <v>132</v>
+      </c>
+      <c r="G28" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="H28" s="26" t="s">
+        <v>134</v>
+      </c>
+      <c r="I28" s="68" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+      <c r="E29" s="96"/>
+      <c r="F29" s="27" t="s">
+        <v>137</v>
+      </c>
+      <c r="G29" s="27" t="s">
+        <v>189</v>
+      </c>
+      <c r="H29" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="I29" s="68" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="E30" s="96"/>
+      <c r="F30" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="G30" s="27" t="s">
+        <v>191</v>
+      </c>
+      <c r="H30" s="28" t="s">
+        <v>192</v>
+      </c>
+      <c r="I30" s="68" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="E31" s="96"/>
+      <c r="F31" s="27" t="s">
+        <v>194</v>
+      </c>
+      <c r="G31" s="27" t="s">
+        <v>195</v>
+      </c>
+      <c r="H31" s="28" t="s">
+        <v>196</v>
+      </c>
+      <c r="I31" s="68" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+      <c r="E32" s="96"/>
+      <c r="F32" s="58" t="s">
+        <v>198</v>
+      </c>
+      <c r="G32" s="58" t="s">
+        <v>199</v>
+      </c>
+      <c r="H32" s="59" t="s">
+        <v>156</v>
+      </c>
+      <c r="I32" s="68" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="33" spans="5:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="E33" s="96"/>
+      <c r="F33" s="27" t="s">
+        <v>158</v>
+      </c>
+      <c r="G33" s="27" t="s">
+        <v>159</v>
+      </c>
+      <c r="H33" s="28" t="s">
+        <v>200</v>
+      </c>
+      <c r="I33" s="68" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="34" spans="5:9" ht="72" x14ac:dyDescent="0.3">
+      <c r="E34" s="98" t="s">
+        <v>202</v>
+      </c>
+      <c r="F34" s="60" t="s">
+        <v>126</v>
+      </c>
+      <c r="G34" s="60" t="s">
+        <v>127</v>
+      </c>
+      <c r="H34" s="61" t="s">
+        <v>128</v>
+      </c>
+      <c r="I34" s="68" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="35" spans="5:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="E35" s="95"/>
+      <c r="F35" s="62" t="s">
+        <v>132</v>
+      </c>
+      <c r="G35" s="62" t="s">
+        <v>133</v>
+      </c>
+      <c r="H35" s="63" t="s">
+        <v>134</v>
+      </c>
+      <c r="I35" s="68" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="36" spans="5:9" ht="72" x14ac:dyDescent="0.3">
+      <c r="E36" s="96"/>
+      <c r="F36" s="27" t="s">
+        <v>137</v>
+      </c>
+      <c r="G36" s="27" t="s">
+        <v>189</v>
+      </c>
+      <c r="H36" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="I36" s="68" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="37" spans="5:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="E37" s="96"/>
+      <c r="F37" s="58" t="s">
+        <v>204</v>
+      </c>
+      <c r="G37" s="58" t="s">
+        <v>133</v>
+      </c>
+      <c r="H37" s="59" t="s">
+        <v>142</v>
+      </c>
+      <c r="I37" s="68" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="38" spans="5:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="E38" s="96"/>
+      <c r="F38" s="27" t="s">
+        <v>205</v>
+      </c>
+      <c r="G38" s="27" t="s">
+        <v>147</v>
+      </c>
+      <c r="H38" s="28" t="s">
+        <v>148</v>
+      </c>
+      <c r="I38" s="68" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="39" spans="5:9" x14ac:dyDescent="0.3">
+      <c r="E39" s="97"/>
+      <c r="F39" s="79" t="s">
+        <v>151</v>
+      </c>
+      <c r="G39" s="81" t="s">
+        <v>152</v>
+      </c>
+      <c r="H39" s="80" t="s">
+        <v>153</v>
+      </c>
+      <c r="I39" s="77"/>
+    </row>
+    <row r="40" spans="5:9" ht="72" x14ac:dyDescent="0.3">
+      <c r="E40" s="98"/>
+      <c r="F40" s="29" t="s">
+        <v>154</v>
+      </c>
+      <c r="G40" s="29" t="s">
+        <v>155</v>
+      </c>
+      <c r="H40" s="30" t="s">
+        <v>186</v>
+      </c>
+      <c r="I40" s="68" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="41" spans="5:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="E41" s="95"/>
+      <c r="F41" s="25" t="s">
+        <v>158</v>
+      </c>
+      <c r="G41" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="H41" s="26" t="s">
+        <v>160</v>
+      </c>
+      <c r="I41" s="68" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="42" spans="5:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="E42" s="96" t="s">
+        <v>206</v>
+      </c>
+      <c r="F42" s="58" t="s">
+        <v>207</v>
+      </c>
+      <c r="G42" s="58" t="s">
+        <v>167</v>
+      </c>
+      <c r="H42" s="59" t="s">
+        <v>148</v>
+      </c>
+      <c r="I42" s="68" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="43" spans="5:9" x14ac:dyDescent="0.3">
+      <c r="E43" s="97"/>
+      <c r="F43" s="79" t="s">
+        <v>208</v>
+      </c>
+      <c r="G43" s="81" t="s">
+        <v>171</v>
+      </c>
+      <c r="H43" s="80" t="s">
+        <v>153</v>
+      </c>
+      <c r="I43" s="77"/>
+    </row>
+    <row r="44" spans="5:9" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="E44" s="96"/>
+      <c r="F44" s="58" t="s">
+        <v>209</v>
+      </c>
+      <c r="G44" s="58" t="s">
+        <v>210</v>
+      </c>
+      <c r="H44" s="59" t="s">
+        <v>211</v>
+      </c>
+      <c r="I44" s="68" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="45" spans="5:9" ht="72" x14ac:dyDescent="0.3">
+      <c r="E45" s="96"/>
+      <c r="F45" s="27" t="s">
+        <v>137</v>
+      </c>
+      <c r="G45" s="27" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="36"/>
-      <c r="B8" s="37" t="s">
-        <v>67</v>
-      </c>
-      <c r="C8" s="38" t="s">
-        <v>68</v>
-      </c>
-      <c r="E8" s="42" t="s">
-        <v>95</v>
-      </c>
-      <c r="F8" s="43" t="s">
-        <v>101</v>
-      </c>
-      <c r="G8" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="H8" s="44" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="30" t="s">
-        <v>69</v>
-      </c>
-      <c r="B9" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="C9" s="32" t="s">
-        <v>71</v>
-      </c>
-      <c r="E9" s="45"/>
-      <c r="F9" s="48" t="s">
-        <v>119</v>
-      </c>
-      <c r="G9" s="48" t="s">
-        <v>120</v>
-      </c>
-      <c r="H9" s="49" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="33"/>
-      <c r="B10" s="34" t="s">
-        <v>72</v>
-      </c>
-      <c r="C10" s="35" t="s">
-        <v>73</v>
-      </c>
-      <c r="E10" s="45"/>
-      <c r="F10" s="46" t="s">
-        <v>107</v>
-      </c>
-      <c r="G10" s="46" t="s">
-        <v>122</v>
-      </c>
-      <c r="H10" s="47" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="33"/>
-      <c r="B11" s="34" t="s">
-        <v>74</v>
-      </c>
-      <c r="C11" s="35" t="s">
-        <v>75</v>
-      </c>
-      <c r="E11" s="45"/>
-      <c r="F11" s="48" t="s">
-        <v>123</v>
-      </c>
-      <c r="G11" s="48" t="s">
-        <v>124</v>
-      </c>
-      <c r="H11" s="49" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="33"/>
-      <c r="B12" s="34" t="s">
-        <v>76</v>
-      </c>
-      <c r="C12" s="35" t="s">
-        <v>77</v>
-      </c>
-      <c r="E12" s="45"/>
-      <c r="F12" s="48" t="s">
-        <v>125</v>
-      </c>
-      <c r="G12" s="48" t="s">
-        <v>126</v>
-      </c>
-      <c r="H12" s="49" t="s">
+      <c r="H45" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="I45" s="68" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="46" spans="5:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="E46" s="98"/>
+      <c r="F46" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="G46" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="H46" s="30" t="s">
+        <v>214</v>
+      </c>
+      <c r="I46" s="68" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="47" spans="5:9" ht="72" x14ac:dyDescent="0.3">
+      <c r="E47" s="71"/>
+      <c r="F47" s="73" t="s">
+        <v>216</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="I47" s="68" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="48" spans="5:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="E48" s="71"/>
+      <c r="F48" s="73" t="s">
+        <v>158</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="I48" s="68" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="49" spans="5:9" ht="72" x14ac:dyDescent="0.3">
+      <c r="E49" s="71" t="s">
+        <v>217</v>
+      </c>
+      <c r="F49" s="73" t="s">
+        <v>218</v>
+      </c>
+      <c r="G49" s="2" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="36"/>
-      <c r="B13" s="37" t="s">
-        <v>78</v>
-      </c>
-      <c r="C13" s="38" t="s">
-        <v>75</v>
-      </c>
-      <c r="E13" s="45"/>
-      <c r="F13" s="46" t="s">
+      <c r="H49" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="G13" s="46" t="s">
-        <v>129</v>
-      </c>
-      <c r="H13" s="47" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="B14" s="31" t="s">
-        <v>55</v>
-      </c>
-      <c r="C14" s="32" t="s">
-        <v>56</v>
-      </c>
-      <c r="E14" s="50"/>
-      <c r="F14" s="51" t="s">
-        <v>130</v>
-      </c>
-      <c r="G14" s="51" t="s">
-        <v>117</v>
-      </c>
-      <c r="H14" s="52" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="33"/>
-      <c r="B15" s="34" t="s">
-        <v>80</v>
-      </c>
-      <c r="C15" s="35" t="s">
-        <v>58</v>
-      </c>
-      <c r="E15" s="42" t="s">
-        <v>96</v>
-      </c>
-      <c r="F15" s="43" t="s">
-        <v>101</v>
-      </c>
-      <c r="G15" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="H15" s="44" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="33"/>
-      <c r="B16" s="34" t="s">
-        <v>63</v>
-      </c>
-      <c r="C16" s="35" t="s">
-        <v>64</v>
-      </c>
-      <c r="E16" s="45"/>
-      <c r="F16" s="46" t="s">
-        <v>104</v>
-      </c>
-      <c r="G16" s="46" t="s">
-        <v>105</v>
-      </c>
-      <c r="H16" s="47" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="36"/>
-      <c r="B17" s="37" t="s">
-        <v>81</v>
-      </c>
-      <c r="C17" s="38" t="s">
-        <v>82</v>
-      </c>
-      <c r="E17" s="45"/>
-      <c r="F17" s="46" t="s">
-        <v>107</v>
-      </c>
-      <c r="G17" s="46" t="s">
-        <v>108</v>
-      </c>
-      <c r="H17" s="47" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="30" t="s">
-        <v>83</v>
-      </c>
-      <c r="B18" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="C18" s="32" t="s">
-        <v>84</v>
-      </c>
-      <c r="E18" s="45"/>
-      <c r="F18" s="48" t="s">
-        <v>110</v>
-      </c>
-      <c r="G18" s="48" t="s">
-        <v>111</v>
-      </c>
-      <c r="H18" s="49" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="33"/>
-      <c r="B19" s="34" t="s">
-        <v>85</v>
-      </c>
-      <c r="C19" s="35" t="s">
-        <v>86</v>
-      </c>
-      <c r="E19" s="45"/>
-      <c r="F19" s="46" t="s">
-        <v>113</v>
-      </c>
-      <c r="G19" s="46" t="s">
-        <v>114</v>
-      </c>
-      <c r="H19" s="47" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="33"/>
-      <c r="B20" s="34" t="s">
-        <v>87</v>
-      </c>
-      <c r="C20" s="35" t="s">
-        <v>82</v>
-      </c>
-      <c r="E20" s="50"/>
-      <c r="F20" s="51" t="s">
-        <v>116</v>
-      </c>
-      <c r="G20" s="51" t="s">
-        <v>117</v>
-      </c>
-      <c r="H20" s="52" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="33"/>
-      <c r="B21" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="C21" s="35" t="s">
-        <v>82</v>
-      </c>
-      <c r="E21" s="42" t="s">
-        <v>132</v>
-      </c>
-      <c r="F21" s="43" t="s">
-        <v>101</v>
-      </c>
-      <c r="G21" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="H21" s="44" t="s">
+      <c r="I49" s="68" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="50" spans="5:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="E50" s="71"/>
+      <c r="F50" s="73" t="s">
+        <v>219</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="I50" s="68" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="51" spans="5:9" x14ac:dyDescent="0.3">
+      <c r="E51" s="82"/>
+      <c r="F51" s="83" t="s">
+        <v>222</v>
+      </c>
+      <c r="G51" s="85" t="s">
+        <v>171</v>
+      </c>
+      <c r="H51" s="84" t="s">
+        <v>153</v>
+      </c>
+      <c r="I51" s="77"/>
+    </row>
+    <row r="52" spans="5:9" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="E52" s="71"/>
+      <c r="F52" s="73" t="s">
+        <v>223</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="I52" s="68" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="53" spans="5:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="E53" s="71"/>
+      <c r="F53" s="73" t="s">
+        <v>141</v>
+      </c>
+      <c r="G53" s="2" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="36"/>
-      <c r="B22" s="37" t="s">
-        <v>89</v>
-      </c>
-      <c r="C22" s="38" t="s">
-        <v>68</v>
-      </c>
-      <c r="E22" s="45"/>
-      <c r="F22" s="46" t="s">
-        <v>104</v>
-      </c>
-      <c r="G22" s="46" t="s">
-        <v>105</v>
-      </c>
-      <c r="H22" s="47" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="30" t="s">
-        <v>90</v>
-      </c>
-      <c r="B23" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="C23" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="E23" s="45"/>
-      <c r="F23" s="46" t="s">
-        <v>107</v>
-      </c>
-      <c r="G23" s="46" t="s">
-        <v>135</v>
-      </c>
-      <c r="H23" s="47" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="36"/>
-      <c r="B24" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="C24" s="38" t="s">
-        <v>92</v>
-      </c>
-      <c r="E24" s="45"/>
-      <c r="F24" s="46" t="s">
-        <v>137</v>
-      </c>
-      <c r="G24" s="46" t="s">
-        <v>105</v>
-      </c>
-      <c r="H24" s="47" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="E25" s="45"/>
-      <c r="F25" s="48" t="s">
-        <v>139</v>
-      </c>
-      <c r="G25" s="48" t="s">
-        <v>120</v>
-      </c>
-      <c r="H25" s="49" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="E26" s="45"/>
-      <c r="F26" s="46" t="s">
-        <v>141</v>
-      </c>
-      <c r="G26" s="46" t="s">
-        <v>122</v>
-      </c>
-      <c r="H26" s="47" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E27" s="50"/>
-      <c r="F27" s="51" t="s">
-        <v>142</v>
-      </c>
-      <c r="G27" s="51" t="s">
-        <v>117</v>
-      </c>
-      <c r="H27" s="52" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="E28" s="42" t="s">
-        <v>143</v>
-      </c>
-      <c r="F28" s="43" t="s">
-        <v>101</v>
-      </c>
-      <c r="G28" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="H28" s="44" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="E29" s="45"/>
-      <c r="F29" s="46" t="s">
-        <v>104</v>
-      </c>
-      <c r="G29" s="46" t="s">
-        <v>105</v>
-      </c>
-      <c r="H29" s="47" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="E30" s="45"/>
-      <c r="F30" s="46" t="s">
-        <v>107</v>
-      </c>
-      <c r="G30" s="46" t="s">
-        <v>135</v>
-      </c>
-      <c r="H30" s="47" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="E31" s="45"/>
-      <c r="F31" s="46" t="s">
-        <v>144</v>
-      </c>
-      <c r="G31" s="46" t="s">
-        <v>105</v>
-      </c>
-      <c r="H31" s="47" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="E32" s="45"/>
-      <c r="F32" s="48" t="s">
-        <v>110</v>
-      </c>
-      <c r="G32" s="48" t="s">
-        <v>111</v>
-      </c>
-      <c r="H32" s="49" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="33" spans="5:8" x14ac:dyDescent="0.3">
-      <c r="E33" s="45"/>
-      <c r="F33" s="46" t="s">
-        <v>113</v>
-      </c>
-      <c r="G33" s="46" t="s">
-        <v>114</v>
-      </c>
-      <c r="H33" s="47" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="34" spans="5:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E34" s="50"/>
-      <c r="F34" s="51" t="s">
-        <v>116</v>
-      </c>
-      <c r="G34" s="51" t="s">
-        <v>117</v>
-      </c>
-      <c r="H34" s="52" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="35" spans="5:8" x14ac:dyDescent="0.3">
-      <c r="E35" s="42" t="s">
-        <v>97</v>
-      </c>
-      <c r="F35" s="53" t="s">
-        <v>145</v>
-      </c>
-      <c r="G35" s="53" t="s">
-        <v>120</v>
-      </c>
-      <c r="H35" s="54" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="36" spans="5:8" x14ac:dyDescent="0.3">
-      <c r="E36" s="45"/>
-      <c r="F36" s="46" t="s">
-        <v>147</v>
-      </c>
-      <c r="G36" s="46" t="s">
-        <v>122</v>
-      </c>
-      <c r="H36" s="47" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="37" spans="5:8" x14ac:dyDescent="0.3">
-      <c r="E37" s="45"/>
-      <c r="F37" s="48" t="s">
-        <v>148</v>
-      </c>
-      <c r="G37" s="48" t="s">
-        <v>149</v>
-      </c>
-      <c r="H37" s="49" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="38" spans="5:8" x14ac:dyDescent="0.3">
-      <c r="E38" s="45"/>
-      <c r="F38" s="46" t="s">
-        <v>151</v>
-      </c>
-      <c r="G38" s="46" t="s">
-        <v>108</v>
-      </c>
-      <c r="H38" s="47" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="39" spans="5:8" x14ac:dyDescent="0.3">
-      <c r="E39" s="45"/>
-      <c r="F39" s="46" t="s">
-        <v>137</v>
-      </c>
-      <c r="G39" s="46" t="s">
-        <v>105</v>
-      </c>
-      <c r="H39" s="47" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="40" spans="5:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E40" s="50"/>
-      <c r="F40" s="55" t="s">
-        <v>154</v>
-      </c>
-      <c r="G40" s="55" t="s">
-        <v>155</v>
-      </c>
-      <c r="H40" s="56" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="41" spans="5:8" x14ac:dyDescent="0.3">
-      <c r="E41" s="42" t="s">
-        <v>98</v>
-      </c>
-      <c r="F41" s="43" t="s">
-        <v>147</v>
-      </c>
-      <c r="G41" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="H41" s="44" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="42" spans="5:8" x14ac:dyDescent="0.3">
-      <c r="E42" s="45"/>
-      <c r="F42" s="48" t="s">
-        <v>158</v>
-      </c>
-      <c r="G42" s="48" t="s">
-        <v>120</v>
-      </c>
-      <c r="H42" s="49" t="s">
+      <c r="H53" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="I53" s="68" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="54" spans="5:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="E54" s="71"/>
+      <c r="F54" s="73" t="s">
+        <v>216</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="I54" s="68" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="55" spans="5:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="E55" s="72"/>
+      <c r="F55" s="74" t="s">
+        <v>181</v>
+      </c>
+      <c r="G55" s="69" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="43" spans="5:8" x14ac:dyDescent="0.3">
-      <c r="E43" s="45"/>
-      <c r="F43" s="46" t="s">
+      <c r="H55" s="69" t="s">
         <v>160</v>
       </c>
-      <c r="G43" s="46" t="s">
-        <v>122</v>
-      </c>
-      <c r="H43" s="47" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="44" spans="5:8" x14ac:dyDescent="0.3">
-      <c r="E44" s="45"/>
-      <c r="F44" s="48" t="s">
+      <c r="I55" s="70" t="s">
         <v>161</v>
       </c>
-      <c r="G44" s="48" t="s">
-        <v>124</v>
-      </c>
-      <c r="H44" s="49" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="45" spans="5:8" x14ac:dyDescent="0.3">
-      <c r="E45" s="45"/>
-      <c r="F45" s="46" t="s">
-        <v>137</v>
-      </c>
-      <c r="G45" s="46" t="s">
-        <v>105</v>
-      </c>
-      <c r="H45" s="47" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="46" spans="5:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E46" s="50"/>
-      <c r="F46" s="55" t="s">
-        <v>154</v>
-      </c>
-      <c r="G46" s="55" t="s">
-        <v>155</v>
-      </c>
-      <c r="H46" s="56" t="s">
-        <v>118</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="14">
     <mergeCell ref="E35:E40"/>
     <mergeCell ref="E41:E46"/>
     <mergeCell ref="E2:E7"/>
@@ -2474,13 +3492,356 @@
     <mergeCell ref="E15:E20"/>
     <mergeCell ref="E21:E27"/>
     <mergeCell ref="E28:E34"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="A23:A24"/>
     <mergeCell ref="A2:A6"/>
     <mergeCell ref="A7:A8"/>
     <mergeCell ref="A9:A13"/>
     <mergeCell ref="A14:A17"/>
     <mergeCell ref="A18:A22"/>
-    <mergeCell ref="A23:A24"/>
   </mergeCells>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:H27"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.21875" style="24" customWidth="1"/>
+    <col min="2" max="2" width="24.44140625" style="24" customWidth="1"/>
+    <col min="3" max="3" width="17.5546875" style="24" customWidth="1"/>
+    <col min="4" max="4" width="24.44140625" style="24" customWidth="1"/>
+    <col min="5" max="6" width="16.5546875" customWidth="1"/>
+    <col min="8" max="8" width="15.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="34"/>
+      <c r="B2" s="35" t="s">
+        <v>94</v>
+      </c>
+      <c r="C2" s="35" t="s">
+        <v>94</v>
+      </c>
+      <c r="D2" s="36" t="s">
+        <v>94</v>
+      </c>
+      <c r="H2" s="50" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="37" t="s">
+        <v>96</v>
+      </c>
+      <c r="B3" s="39" t="s">
+        <v>97</v>
+      </c>
+      <c r="C3" s="39" t="s">
+        <v>98</v>
+      </c>
+      <c r="D3" s="38" t="s">
+        <v>99</v>
+      </c>
+      <c r="H3" s="49" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="40">
+        <v>0.22916666666666666</v>
+      </c>
+      <c r="B4" s="41" t="s">
+        <v>101</v>
+      </c>
+      <c r="C4" s="41" t="s">
+        <v>101</v>
+      </c>
+      <c r="D4" s="42" t="s">
+        <v>101</v>
+      </c>
+      <c r="H4" s="52" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="44">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="B5" s="41" t="s">
+        <v>103</v>
+      </c>
+      <c r="C5" s="41" t="s">
+        <v>103</v>
+      </c>
+      <c r="D5" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="H5" s="53" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="44">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="B6" s="41" t="s">
+        <v>105</v>
+      </c>
+      <c r="C6" s="41" t="s">
+        <v>105</v>
+      </c>
+      <c r="D6" s="42" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="44">
+        <v>0.375</v>
+      </c>
+      <c r="B7" s="51" t="s">
+        <v>106</v>
+      </c>
+      <c r="C7" s="41" t="s">
+        <v>106</v>
+      </c>
+      <c r="D7" s="42" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="44">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="B8" s="51" t="s">
+        <v>110</v>
+      </c>
+      <c r="C8" s="51" t="s">
+        <v>107</v>
+      </c>
+      <c r="D8" s="54" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="44">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="B9" s="51" t="s">
+        <v>106</v>
+      </c>
+      <c r="C9" s="51" t="s">
+        <v>106</v>
+      </c>
+      <c r="D9" s="42" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="44">
+        <v>0.75</v>
+      </c>
+      <c r="B10" s="51" t="s">
+        <v>108</v>
+      </c>
+      <c r="C10" s="102" t="s">
+        <v>102</v>
+      </c>
+      <c r="D10" s="42" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="44">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="B11" s="104" t="s">
+        <v>100</v>
+      </c>
+      <c r="C11" s="102"/>
+      <c r="D11" s="103" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="44">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="B12" s="104"/>
+      <c r="C12" s="51" t="s">
+        <v>109</v>
+      </c>
+      <c r="D12" s="103"/>
+    </row>
+    <row r="13" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="47">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="B13" s="24" t="s">
+        <v>111</v>
+      </c>
+      <c r="C13" s="48" t="s">
+        <v>111</v>
+      </c>
+      <c r="D13" s="46" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="40" t="s">
+        <v>112</v>
+      </c>
+      <c r="B14" s="57" t="s">
+        <v>113</v>
+      </c>
+      <c r="C14" s="56" t="s">
+        <v>113</v>
+      </c>
+      <c r="D14" s="43" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="47" t="s">
+        <v>112</v>
+      </c>
+      <c r="B15" s="55" t="s">
+        <v>114</v>
+      </c>
+      <c r="C15" s="48" t="s">
+        <v>114</v>
+      </c>
+      <c r="D15" s="45" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="17" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="34"/>
+      <c r="B17" s="35" t="s">
+        <v>115</v>
+      </c>
+      <c r="C17" s="36" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="37" t="s">
+        <v>96</v>
+      </c>
+      <c r="B18" s="39" t="s">
+        <v>116</v>
+      </c>
+      <c r="C18" s="38" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="40">
+        <v>0.22916666666666666</v>
+      </c>
+      <c r="B19" s="51" t="s">
+        <v>104</v>
+      </c>
+      <c r="C19" s="42" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="44">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="B20" s="41" t="s">
+        <v>106</v>
+      </c>
+      <c r="C20" s="42" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="44">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="B21" s="51" t="s">
+        <v>230</v>
+      </c>
+      <c r="C21" s="54" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="44">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="B22" s="41" t="s">
+        <v>106</v>
+      </c>
+      <c r="C22" s="42" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="44">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="B23" s="24" t="s">
+        <v>119</v>
+      </c>
+      <c r="C23" s="103" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="44">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="B24" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="C24" s="103"/>
+    </row>
+    <row r="25" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="47">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="B25" s="24" t="s">
+        <v>111</v>
+      </c>
+      <c r="C25" s="46" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="100" t="s">
+        <v>112</v>
+      </c>
+      <c r="B26" s="56" t="s">
+        <v>113</v>
+      </c>
+      <c r="C26" s="43" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="101"/>
+      <c r="B27" s="48" t="s">
+        <v>114</v>
+      </c>
+      <c r="C27" s="45" t="s">
+        <v>114</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C23:C24"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Dieta.xlsx
+++ b/Dieta.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calculadora" sheetId="1" r:id="R4f70359fb9d1439a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Referências" sheetId="2" r:id="R8ab76e1291124fae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dieta" sheetId="3" r:id="R6b4925c517cc466b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rotina" sheetId="4" r:id="Rc7593e02655947b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calculadora" sheetId="1" r:id="Rf3df1ed0e51f4cd5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Referências" sheetId="2" r:id="R0fd7fdec182f4b39"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dieta" sheetId="3" r:id="R0968e2cb2cc448b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rotina" sheetId="4" r:id="R02598b9b04c04542"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -254,16 +254,6 @@
     <x:t xml:space="preserve">Almoço</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Arroz + feijão + frango + legumes + abacate</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Arroz cozido|350 g
-Feijão cozido|150 g
-Frango|120 g
-Legumes/salada|200 g
-Abacate|100 g</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">~75 g/dia</x:t>
   </x:si>
   <x:si>
@@ -342,23 +332,10 @@
     <x:t xml:space="preserve">Jantar / pós</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Arroz + feijão + carne + batata + legumes</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Arroz cozido|300 g
-Feijão|100 g
-Carne bovina magra|120 g
-Batata cozida/assada|100 g
-Legumes/salada|200 g</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">3. Almoço</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Arroz cozido</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">250 g</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">22h30</x:t>
@@ -372,12 +349,6 @@
   <x:si>
     <x:t xml:space="preserve">Leite|250 ml
 Manga|150 g</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Feijão cozido</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">150 g</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Terça</x:t>
@@ -393,19 +364,7 @@
 Banana|1 média</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Frango</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">~80 g</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">10h15</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Brócolis + couve-flor + alface</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">à vontade / ~200 g</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">11h20</x:t>
@@ -421,9 +380,6 @@
 Banana|1 média</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Abacate</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">12h00–13h00</x:t>
   </x:si>
   <x:si>
@@ -437,13 +393,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Almoço / pós</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Arroz cozido|350 g
-Feijão cozido|150 g
-Frango|120 g
-Legumes/salada|200 g
-Abacate|80 g</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Muçarela ou queijo prato</x:t>
@@ -472,26 +421,10 @@
     <x:t xml:space="preserve">20h15</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Arroz cozido|300 g
-Feijão|100 g
-Carne bovina magra|120 g
-Batata|100 g
-Legumes/salada|200 g</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">5. Jantar / pós-treino</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">200 g</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">22h15</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Feijão</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">100 g</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Quarta</x:t>
@@ -504,25 +437,6 @@
 Banana|1 média</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Carne bovina magra</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Batata cozida/assada</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Arroz + feijão + carne + legumes + abacate</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Arroz cozido|350 g
-Feijão|150 g
-Carne bovina magra|120 g
-Legumes/salada|200 g
-Abacate|100 g</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Brócolis/couve-flor/alface</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">6. Ceia</x:t>
   </x:si>
   <x:si>
@@ -532,27 +446,10 @@
     <x:t xml:space="preserve">~150 g</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Arroz + feijão + frango + batata + legumes</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Arroz cozido|300 g
-Feijão|100 g
-Frango|120 g
-Batata|100 g
-Legumes/salada|200 g</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Quinta — presencial</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Marmita</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Arroz cozido|350 g
-Feijão|150 g
-Frango|120 g
-Legumes|200 g
-Abacate|80 g</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Lanche no trabalho</x:t>
@@ -594,13 +491,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Sexta — presencial</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Arroz cozido|350 g
-Feijão|150 g
-Carne bovina magra|120 g
-Legumes|200 g
-Abacate|80 g</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">16h15</x:t>
@@ -635,13 +525,6 @@
 Whey|30 g</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Arroz cozido|350 g
-Feijão|150 g
-Frango|120 g
-Legumes/salada|200 g
-Abacate|100 g</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Pão + queijo + banana + uva</x:t>
   </x:si>
   <x:si>
@@ -676,32 +559,12 @@
     <x:t xml:space="preserve">12h30</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Arroz + feijão + carne + batata + legumes + abacate</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Arroz cozido|350 g
-Feijão|150 g
-Carne bovina magra|120 g
-Batata|100 g
-Legumes/salada|200 g
-Abacate|80 g</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Whey + mamão + pão</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Whey|30 g
 Mamão|200 g
 Pão|2 fatias</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Arroz + feijão + frango + legumes</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Arroz cozido|300 g
-Feijão|100 g
-Frango|120 g
-Legumes/salada|200 g</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">em casa</x:t>
@@ -2514,153 +2377,159 @@
       <x:c r="G4" s="27" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="H4" s="28" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="I4" s="68" t="s">
-        <x:v>79</x:v>
+      <x:c r="H4" s="28" t="str">
+        <x:v>Arroz + frango + legumes + abacate</x:v>
+      </x:c>
+      <x:c r="I4" s="68" t="str">
+        <x:v>Arroz cozido|410 g
+Frango|135 g
+Legumes/salada|300 g
+Abacate|100 g</x:v>
       </x:c>
       <x:c r="K4" s="2" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="L4" s="2" t="s">
-        <x:v>80</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="43.20000076293945">
       <x:c r="A5" s="94"/>
       <x:c r="B5" s="27" t="s">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C5" s="28" t="s">
-        <x:v>82</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E5" s="96"/>
       <x:c r="F5" s="58" t="s">
-        <x:v>83</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="G5" s="58" t="s">
         <x:v>72</x:v>
       </x:c>
       <x:c r="H5" s="59" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="I5" s="68" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="K5" s="2" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="I5" s="68" t="s">
+      <x:c r="L5" s="2" t="s">
         <x:v>85</x:v>
-      </x:c>
-      <x:c r="K5" s="2" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="L5" s="2" t="s">
-        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="28.799999237060547">
       <x:c r="A6" s="93"/>
       <x:c r="B6" s="29" t="s">
-        <x:v>88</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C6" s="30" t="s">
-        <x:v>89</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E6" s="96"/>
       <x:c r="F6" s="27" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="G6" s="27" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="H6" s="28" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="G6" s="27" t="s">
+      <x:c r="I6" s="68" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="H6" s="28" t="s">
+      <x:c r="K6" s="2" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="I6" s="68" t="s">
+      <x:c r="L6" s="2" t="s">
         <x:v>93</x:v>
-      </x:c>
-      <x:c r="K6" s="2" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="L6" s="2" t="s">
-        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="92" t="s">
-        <x:v>96</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B7" s="25" t="s">
-        <x:v>97</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C7" s="26" t="s">
         <x:v>70</x:v>
       </x:c>
       <x:c r="E7" s="99"/>
       <x:c r="F7" s="75" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="G7" s="78" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="H7" s="76" t="s">
         <x:v>98</x:v>
-      </x:c>
-      <x:c r="G7" s="78" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="H7" s="76" t="s">
-        <x:v>100</x:v>
       </x:c>
       <x:c r="I7" s="77"/>
     </x:row>
     <x:row r="8" ht="72">
       <x:c r="A8" s="93"/>
       <x:c r="B8" s="29" t="s">
-        <x:v>101</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C8" s="30" t="s">
-        <x:v>102</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E8" s="95"/>
       <x:c r="F8" s="25" t="s">
-        <x:v>103</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="G8" s="25" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="H8" s="26" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="I8" s="68" t="s">
-        <x:v>106</x:v>
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="H8" s="26" t="str">
+        <x:v>Arroz + carne + batata + legumes</x:v>
+      </x:c>
+      <x:c r="I8" s="68" t="str">
+        <x:v>Arroz cozido|335 g
+Carne bovina magra|127 g
+Batata cozida/assada|100 g
+Legumes/salada|300 g</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="28.799999237060547">
       <x:c r="A9" s="92" t="s">
-        <x:v>107</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B9" s="25" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="C9" s="26" t="s">
-        <x:v>109</x:v>
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="C9" s="26" t="str">
+        <x:v>310 g</x:v>
       </x:c>
       <x:c r="E9" s="96"/>
       <x:c r="F9" s="58" t="s">
-        <x:v>110</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G9" s="58" t="s">
-        <x:v>111</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="H9" s="59" t="s">
-        <x:v>112</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="I9" s="68" t="s">
-        <x:v>113</x:v>
+        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="72">
       <x:c r="A10" s="94"/>
-      <x:c r="B10" s="27" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="C10" s="28" t="s">
-        <x:v>115</x:v>
+      <x:c r="B10" s="27" t="str">
+        <x:v>Frango</x:v>
+      </x:c>
+      <x:c r="C10" s="28" t="str">
+        <x:v>~95 g</x:v>
       </x:c>
       <x:c r="E10" s="96" t="s">
-        <x:v>116</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="F10" s="27" t="s">
         <x:v>63</x:v>
@@ -2669,23 +2538,23 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="H10" s="28" t="s">
-        <x:v>117</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="I10" s="68" t="s">
-        <x:v>118</x:v>
+        <x:v>111</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="28.799999237060547">
       <x:c r="A11" s="94"/>
-      <x:c r="B11" s="27" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="C11" s="28" t="s">
-        <x:v>120</x:v>
+      <x:c r="B11" s="27" t="str">
+        <x:v>Brócolis + couve-flor + alface</x:v>
+      </x:c>
+      <x:c r="C11" s="28" t="str">
+        <x:v>~300 g</x:v>
       </x:c>
       <x:c r="E11" s="96"/>
       <x:c r="F11" s="58" t="s">
-        <x:v>121</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="G11" s="58" t="s">
         <x:v>72</x:v>
@@ -2702,49 +2571,45 @@
     </x:row>
     <x:row r="12" ht="28.799999237060547">
       <x:c r="A12" s="94"/>
-      <x:c r="B12" s="27" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="C12" s="28" t="s">
-        <x:v>123</x:v>
+      <x:c r="B12" s="27" t="str">
+        <x:v>Abacate</x:v>
+      </x:c>
+      <x:c r="C12" s="28" t="str">
+        <x:v>~80 g</x:v>
       </x:c>
       <x:c r="E12" s="96"/>
       <x:c r="F12" s="58" t="s">
-        <x:v>124</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="G12" s="58" t="s">
-        <x:v>125</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="H12" s="59" t="s">
-        <x:v>126</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="I12" s="68" t="s">
-        <x:v>127</x:v>
+        <x:v>116</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="93"/>
-      <x:c r="B13" s="29" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="C13" s="30" t="s">
-        <x:v>120</x:v>
-      </x:c>
+      <x:c r="B13" s="29" t="str"/>
+      <x:c r="C13" s="30" t="str"/>
       <x:c r="E13" s="97"/>
       <x:c r="F13" s="79" t="s">
-        <x:v>129</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="G13" s="81" t="s">
-        <x:v>130</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="H13" s="80" t="s">
-        <x:v>100</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="I13" s="77"/>
     </x:row>
     <x:row r="14" ht="72">
       <x:c r="A14" s="92" t="s">
-        <x:v>131</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B14" s="25" t="s">
         <x:v>60</x:v>
@@ -2754,116 +2619,122 @@
       </x:c>
       <x:c r="E14" s="98"/>
       <x:c r="F14" s="60" t="s">
-        <x:v>132</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="G14" s="60" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="H14" s="61" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="I14" s="68" t="s">
-        <x:v>134</x:v>
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="H14" s="61" t="str">
+        <x:v>Arroz + frango + legumes + abacate</x:v>
+      </x:c>
+      <x:c r="I14" s="68" t="str">
+        <x:v>Arroz cozido|410 g
+Frango|135 g
+Legumes/salada|300 g
+Abacate|80 g</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="43.20000076293945">
       <x:c r="A15" s="94"/>
       <x:c r="B15" s="27" t="s">
-        <x:v>135</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C15" s="28" t="s">
         <x:v>70</x:v>
       </x:c>
       <x:c r="E15" s="95"/>
       <x:c r="F15" s="25" t="s">
-        <x:v>83</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="G15" s="25" t="s">
-        <x:v>136</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H15" s="26" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="I15" s="68" t="s">
-        <x:v>137</x:v>
+        <x:v>124</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="94"/>
       <x:c r="B16" s="27" t="s">
-        <x:v>88</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C16" s="28" t="s">
-        <x:v>89</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E16" s="97"/>
       <x:c r="F16" s="79" t="s">
-        <x:v>138</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="G16" s="81" t="s">
-        <x:v>139</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="H16" s="80" t="s">
-        <x:v>100</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="I16" s="77"/>
     </x:row>
     <x:row r="17" ht="72">
       <x:c r="A17" s="93"/>
       <x:c r="B17" s="29" t="s">
-        <x:v>140</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C17" s="30" t="s">
-        <x:v>141</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="E17" s="96"/>
       <x:c r="F17" s="27" t="s">
-        <x:v>142</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="G17" s="27" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="H17" s="28" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="I17" s="68" t="s">
-        <x:v>143</x:v>
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="H17" s="28" t="str">
+        <x:v>Arroz + carne + batata + legumes</x:v>
+      </x:c>
+      <x:c r="I17" s="68" t="str">
+        <x:v>Arroz cozido|335 g
+Carne bovina magra|127 g
+Batata|100 g
+Legumes/salada|300 g</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="28.799999237060547">
       <x:c r="A18" s="92" t="s">
-        <x:v>144</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B18" s="25" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="C18" s="26" t="s">
-        <x:v>145</x:v>
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="C18" s="26" t="str">
+        <x:v>235 g</x:v>
       </x:c>
       <x:c r="E18" s="96"/>
       <x:c r="F18" s="58" t="s">
-        <x:v>146</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="G18" s="58" t="s">
-        <x:v>111</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="H18" s="59" t="s">
-        <x:v>112</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="I18" s="68" t="s">
-        <x:v>113</x:v>
+        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="72">
       <x:c r="A19" s="94"/>
-      <x:c r="B19" s="27" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="C19" s="28" t="s">
-        <x:v>148</x:v>
+      <x:c r="B19" s="27" t="str">
+        <x:v>Carne bovina magra</x:v>
+      </x:c>
+      <x:c r="C19" s="28" t="str">
+        <x:v>~107 g</x:v>
       </x:c>
       <x:c r="E19" s="96" t="s">
-        <x:v>149</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="F19" s="27" t="s">
         <x:v>63</x:v>
@@ -2875,16 +2746,16 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="I19" s="68" t="s">
-        <x:v>150</x:v>
+        <x:v>133</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="28.799999237060547">
       <x:c r="A20" s="94"/>
-      <x:c r="B20" s="27" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="C20" s="28" t="s">
-        <x:v>141</x:v>
+      <x:c r="B20" s="27" t="str">
+        <x:v>Batata cozida/assada</x:v>
+      </x:c>
+      <x:c r="C20" s="28" t="str">
+        <x:v>~100 g</x:v>
       </x:c>
       <x:c r="E20" s="98"/>
       <x:c r="F20" s="60" t="s">
@@ -2905,11 +2776,11 @@
     </x:row>
     <x:row r="21" ht="72">
       <x:c r="A21" s="94"/>
-      <x:c r="B21" s="27" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="C21" s="28" t="s">
-        <x:v>141</x:v>
+      <x:c r="B21" s="27" t="str">
+        <x:v>Brócolis/couve-flor/alface</x:v>
+      </x:c>
+      <x:c r="C21" s="28" t="str">
+        <x:v>~300 g</x:v>
       </x:c>
       <x:c r="E21" s="95"/>
       <x:c r="F21" s="25" t="s">
@@ -2918,38 +2789,37 @@
       <x:c r="G21" s="25" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="H21" s="26" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="I21" s="68" t="s">
-        <x:v>154</x:v>
+      <x:c r="H21" s="26" t="str">
+        <x:v>Arroz + carne + legumes + abacate</x:v>
+      </x:c>
+      <x:c r="I21" s="68" t="str">
+        <x:v>Arroz cozido|405 g
+Carne bovina magra|132 g
+Legumes/salada|300 g
+Abacate|100 g</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="43.20000076293945">
       <x:c r="A22" s="93"/>
-      <x:c r="B22" s="29" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="C22" s="30" t="s">
-        <x:v>102</x:v>
-      </x:c>
+      <x:c r="B22" s="29" t="str"/>
+      <x:c r="C22" s="30" t="str"/>
       <x:c r="E22" s="96"/>
       <x:c r="F22" s="27" t="s">
-        <x:v>83</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="G22" s="27" t="s">
         <x:v>72</x:v>
       </x:c>
       <x:c r="H22" s="28" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="I22" s="68" t="s">
-        <x:v>85</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="28.799999237060547">
       <x:c r="A23" s="92" t="s">
-        <x:v>156</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B23" s="25" t="s">
         <x:v>74</x:v>
@@ -2959,71 +2829,74 @@
       </x:c>
       <x:c r="E23" s="96"/>
       <x:c r="F23" s="27" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="G23" s="27" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="H23" s="28" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="G23" s="27" t="s">
+      <x:c r="I23" s="68" t="s">
         <x:v>91</x:v>
-      </x:c>
-      <x:c r="H23" s="28" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="I23" s="68" t="s">
-        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="93"/>
       <x:c r="B24" s="29" t="s">
-        <x:v>157</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C24" s="30" t="s">
-        <x:v>158</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="E24" s="97"/>
       <x:c r="F24" s="79" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="G24" s="81" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="H24" s="80" t="s">
         <x:v>98</x:v>
-      </x:c>
-      <x:c r="G24" s="81" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="H24" s="80" t="s">
-        <x:v>100</x:v>
       </x:c>
       <x:c r="I24" s="77"/>
     </x:row>
     <x:row r="25" ht="72">
       <x:c r="E25" s="96"/>
       <x:c r="F25" s="58" t="s">
-        <x:v>103</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="G25" s="58" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="H25" s="59" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="I25" s="68" t="s">
-        <x:v>160</x:v>
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="H25" s="59" t="str">
+        <x:v>Arroz + frango + batata + legumes</x:v>
+      </x:c>
+      <x:c r="I25" s="68" t="str">
+        <x:v>Arroz cozido|335 g
+Frango|128 g
+Batata|100 g
+Legumes/salada|300 g</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="28.799999237060547">
       <x:c r="E26" s="96"/>
       <x:c r="F26" s="27" t="s">
-        <x:v>110</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G26" s="27" t="s">
-        <x:v>111</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="H26" s="28" t="s">
-        <x:v>112</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="I26" s="68" t="s">
-        <x:v>113</x:v>
+        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="72">
       <x:c r="E27" s="98" t="s">
-        <x:v>161</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="F27" s="60" t="s">
         <x:v>63</x:v>
@@ -3035,7 +2908,7 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="I27" s="68" t="s">
-        <x:v>150</x:v>
+        <x:v>133</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="28.799999237060547">
@@ -3062,78 +2935,84 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="G29" s="27" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="H29" s="28" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="I29" s="68" t="s">
-        <x:v>163</x:v>
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="H29" s="28" t="str">
+        <x:v>Arroz + frango + legumes + abacate</x:v>
+      </x:c>
+      <x:c r="I29" s="68" t="str">
+        <x:v>Arroz cozido|410 g
+Frango|135 g
+Legumes|300 g
+Abacate|80 g</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="43.20000076293945">
       <x:c r="E30" s="96"/>
       <x:c r="F30" s="27" t="s">
-        <x:v>83</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="G30" s="27" t="s">
-        <x:v>164</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="H30" s="28" t="s">
-        <x:v>165</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="I30" s="68" t="s">
-        <x:v>166</x:v>
+        <x:v>141</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="43.20000076293945">
       <x:c r="E31" s="96"/>
       <x:c r="F31" s="27" t="s">
-        <x:v>167</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="G31" s="27" t="s">
-        <x:v>168</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="H31" s="28" t="s">
-        <x:v>169</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="I31" s="68" t="s">
-        <x:v>170</x:v>
+        <x:v>145</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="72">
       <x:c r="E32" s="96"/>
       <x:c r="F32" s="58" t="s">
-        <x:v>171</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="G32" s="58" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="H32" s="59" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="I32" s="68" t="s">
-        <x:v>143</x:v>
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="H32" s="59" t="str">
+        <x:v>Arroz + carne + batata + legumes</x:v>
+      </x:c>
+      <x:c r="I32" s="68" t="str">
+        <x:v>Arroz cozido|335 g
+Carne bovina magra|127 g
+Batata|100 g
+Legumes/salada|300 g</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="28.799999237060547">
       <x:c r="E33" s="96"/>
       <x:c r="F33" s="27" t="s">
-        <x:v>110</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G33" s="27" t="s">
-        <x:v>111</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="H33" s="28" t="s">
-        <x:v>173</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="I33" s="68" t="s">
-        <x:v>174</x:v>
+        <x:v>149</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="72">
       <x:c r="E34" s="98" t="s">
-        <x:v>175</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="F34" s="60" t="s">
         <x:v>63</x:v>
@@ -3145,7 +3024,7 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="I34" s="68" t="s">
-        <x:v>150</x:v>
+        <x:v>133</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="28.799999237060547">
@@ -3172,131 +3051,137 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="G36" s="27" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="H36" s="28" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="I36" s="68" t="s">
-        <x:v>176</x:v>
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="H36" s="28" t="str">
+        <x:v>Arroz + carne + legumes + abacate</x:v>
+      </x:c>
+      <x:c r="I36" s="68" t="str">
+        <x:v>Arroz cozido|405 g
+Carne bovina magra|132 g
+Legumes|300 g
+Abacate|80 g</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="43.20000076293945">
       <x:c r="E37" s="96"/>
       <x:c r="F37" s="58" t="s">
-        <x:v>177</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="G37" s="58" t="s">
         <x:v>72</x:v>
       </x:c>
       <x:c r="H37" s="59" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="I37" s="68" t="s">
-        <x:v>85</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="28.799999237060547">
       <x:c r="E38" s="96"/>
       <x:c r="F38" s="27" t="s">
-        <x:v>178</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="G38" s="27" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="H38" s="28" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="I38" s="68" t="s">
         <x:v>91</x:v>
-      </x:c>
-      <x:c r="H38" s="28" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="I38" s="68" t="s">
-        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
       <x:c r="E39" s="97"/>
       <x:c r="F39" s="79" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="G39" s="81" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="H39" s="80" t="s">
         <x:v>98</x:v>
-      </x:c>
-      <x:c r="G39" s="81" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="H39" s="80" t="s">
-        <x:v>100</x:v>
       </x:c>
       <x:c r="I39" s="77"/>
     </x:row>
     <x:row r="40" ht="72">
       <x:c r="E40" s="98"/>
       <x:c r="F40" s="29" t="s">
-        <x:v>103</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="G40" s="29" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="H40" s="30" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="I40" s="68" t="s">
-        <x:v>160</x:v>
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="H40" s="30" t="str">
+        <x:v>Arroz + frango + batata + legumes</x:v>
+      </x:c>
+      <x:c r="I40" s="68" t="str">
+        <x:v>Arroz cozido|335 g
+Frango|128 g
+Batata|100 g
+Legumes/salada|300 g</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="28.799999237060547">
       <x:c r="E41" s="95"/>
       <x:c r="F41" s="25" t="s">
-        <x:v>110</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G41" s="25" t="s">
-        <x:v>111</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="H41" s="26" t="s">
-        <x:v>112</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="I41" s="68" t="s">
-        <x:v>113</x:v>
+        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="28.799999237060547">
       <x:c r="E42" s="96" t="s">
-        <x:v>179</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="F42" s="58" t="s">
-        <x:v>180</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="G42" s="58" t="s">
-        <x:v>125</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="H42" s="59" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="I42" s="68" t="s">
-        <x:v>93</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="E43" s="97"/>
       <x:c r="F43" s="79" t="s">
-        <x:v>181</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="G43" s="81" t="s">
-        <x:v>130</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="H43" s="80" t="s">
-        <x:v>100</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="I43" s="77"/>
     </x:row>
     <x:row r="44" ht="86.4000015258789">
       <x:c r="E44" s="96"/>
       <x:c r="F44" s="58" t="s">
-        <x:v>182</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="G44" s="58" t="s">
-        <x:v>183</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="H44" s="59" t="s">
-        <x:v>184</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="I44" s="68" t="s">
-        <x:v>185</x:v>
+        <x:v>159</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="72">
@@ -3307,64 +3192,70 @@
       <x:c r="G45" s="27" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="H45" s="28" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="I45" s="68" t="s">
-        <x:v>186</x:v>
+      <x:c r="H45" s="28" t="str">
+        <x:v>Arroz + frango + legumes + abacate</x:v>
+      </x:c>
+      <x:c r="I45" s="68" t="str">
+        <x:v>Arroz cozido|410 g
+Frango|135 g
+Legumes/salada|300 g
+Abacate|100 g</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="57.599998474121094">
       <x:c r="E46" s="98"/>
       <x:c r="F46" s="29" t="s">
-        <x:v>83</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="G46" s="29" t="s">
         <x:v>72</x:v>
       </x:c>
       <x:c r="H46" s="30" t="s">
-        <x:v>187</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="I46" s="68" t="s">
-        <x:v>188</x:v>
+        <x:v>161</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="72">
       <x:c r="E47" s="71"/>
       <x:c r="F47" s="73" t="s">
-        <x:v>189</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="G47" s="2" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="H47" s="2" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="I47" s="68" t="s">
-        <x:v>143</x:v>
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="H47" s="2" t="str">
+        <x:v>Arroz + carne + batata + legumes</x:v>
+      </x:c>
+      <x:c r="I47" s="68" t="str">
+        <x:v>Arroz cozido|335 g
+Carne bovina magra|127 g
+Batata|100 g
+Legumes/salada|300 g</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="28.799999237060547">
       <x:c r="E48" s="71"/>
       <x:c r="F48" s="73" t="s">
-        <x:v>110</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G48" s="2" t="s">
-        <x:v>111</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="H48" s="2" t="s">
-        <x:v>112</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="I48" s="68" t="s">
-        <x:v>113</x:v>
+        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="72">
       <x:c r="E49" s="71" t="s">
-        <x:v>190</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="F49" s="73" t="s">
-        <x:v>191</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="G49" s="2" t="s">
         <x:v>64</x:v>
@@ -3373,95 +3264,101 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="I49" s="68" t="s">
-        <x:v>150</x:v>
+        <x:v>133</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="28.799999237060547">
       <x:c r="E50" s="71"/>
       <x:c r="F50" s="73" t="s">
-        <x:v>192</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="G50" s="2" t="s">
-        <x:v>125</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="H50" s="2" t="s">
-        <x:v>193</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="I50" s="68" t="s">
-        <x:v>194</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
       <x:c r="E51" s="82"/>
       <x:c r="F51" s="83" t="s">
-        <x:v>195</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="G51" s="85" t="s">
-        <x:v>130</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="H51" s="84" t="s">
-        <x:v>100</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="I51" s="77"/>
     </x:row>
     <x:row r="52" ht="86.4000015258789">
       <x:c r="E52" s="71"/>
       <x:c r="F52" s="73" t="s">
-        <x:v>196</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="G52" s="2" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="H52" s="2" t="s">
-        <x:v>197</x:v>
-      </x:c>
-      <x:c r="I52" s="68" t="s">
-        <x:v>198</x:v>
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="H52" s="2" t="str">
+        <x:v>Arroz + carne + batata + legumes + abacate</x:v>
+      </x:c>
+      <x:c r="I52" s="68" t="str">
+        <x:v>Arroz cozido|405 g
+Carne bovina magra|132 g
+Batata|100 g
+Legumes/salada|300 g
+Abacate|80 g</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="43.20000076293945">
       <x:c r="E53" s="71"/>
       <x:c r="F53" s="73" t="s">
-        <x:v>83</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="G53" s="2" t="s">
         <x:v>72</x:v>
       </x:c>
       <x:c r="H53" s="2" t="s">
-        <x:v>199</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="I53" s="68" t="s">
-        <x:v>200</x:v>
+        <x:v>171</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="57.599998474121094">
       <x:c r="E54" s="71"/>
       <x:c r="F54" s="73" t="s">
-        <x:v>189</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="G54" s="2" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="H54" s="2" t="s">
-        <x:v>201</x:v>
-      </x:c>
-      <x:c r="I54" s="68" t="s">
-        <x:v>202</x:v>
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="H54" s="2" t="str">
+        <x:v>Arroz + frango + legumes</x:v>
+      </x:c>
+      <x:c r="I54" s="68" t="str">
+        <x:v>Arroz cozido|335 g
+Frango|128 g
+Legumes/salada|300 g</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="28.799999237060547">
       <x:c r="E55" s="72"/>
       <x:c r="F55" s="74" t="s">
-        <x:v>146</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="G55" s="69" t="s">
-        <x:v>111</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="H55" s="69" t="s">
-        <x:v>112</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="I55" s="70" t="s">
-        <x:v>113</x:v>
+        <x:v>108</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3501,33 +3398,33 @@
     <x:row r="2">
       <x:c r="A2" s="34"/>
       <x:c r="B2" s="35" t="s">
-        <x:v>203</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="C2" s="35" t="s">
-        <x:v>203</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="D2" s="36" t="s">
-        <x:v>203</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="H2" s="50" t="s">
-        <x:v>204</x:v>
+        <x:v>173</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="37" t="s">
-        <x:v>205</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="B3" s="39" t="s">
-        <x:v>206</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="C3" s="39" t="s">
-        <x:v>207</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="D3" s="38" t="s">
-        <x:v>208</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="H3" s="49" t="s">
-        <x:v>209</x:v>
+        <x:v>178</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -3535,16 +3432,16 @@
         <x:v>0.22916666666666666</x:v>
       </x:c>
       <x:c r="B4" s="41" t="s">
-        <x:v>210</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="C4" s="41" t="s">
-        <x:v>210</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="D4" s="42" t="s">
-        <x:v>210</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="H4" s="52" t="s">
-        <x:v>211</x:v>
+        <x:v>180</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -3552,16 +3449,16 @@
         <x:v>0.27083333333333331</x:v>
       </x:c>
       <x:c r="B5" s="41" t="s">
-        <x:v>212</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="C5" s="41" t="s">
-        <x:v>212</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="D5" s="42" t="s">
-        <x:v>212</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="H5" s="53" t="s">
-        <x:v>213</x:v>
+        <x:v>182</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -3569,13 +3466,13 @@
         <x:v>0.33333333333333331</x:v>
       </x:c>
       <x:c r="B6" s="41" t="s">
-        <x:v>214</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="C6" s="41" t="s">
-        <x:v>214</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="D6" s="42" t="s">
-        <x:v>214</x:v>
+        <x:v>183</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -3583,13 +3480,13 @@
         <x:v>0.375</x:v>
       </x:c>
       <x:c r="B7" s="51" t="s">
-        <x:v>215</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="C7" s="41" t="s">
-        <x:v>215</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="D7" s="42" t="s">
-        <x:v>215</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -3597,13 +3494,13 @@
         <x:v>0.54166666666666663</x:v>
       </x:c>
       <x:c r="B8" s="51" t="s">
-        <x:v>216</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C8" s="51" t="s">
-        <x:v>217</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="D8" s="54" t="s">
-        <x:v>216</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -3611,13 +3508,13 @@
         <x:v>0.58333333333333337</x:v>
       </x:c>
       <x:c r="B9" s="51" t="s">
-        <x:v>215</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="C9" s="51" t="s">
-        <x:v>215</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="D9" s="42" t="s">
-        <x:v>215</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -3625,13 +3522,13 @@
         <x:v>0.75</x:v>
       </x:c>
       <x:c r="B10" s="51" t="s">
-        <x:v>218</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C10" s="102" t="s">
-        <x:v>211</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="D10" s="42" t="s">
-        <x:v>218</x:v>
+        <x:v>187</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -3639,11 +3536,11 @@
         <x:v>0.79166666666666663</x:v>
       </x:c>
       <x:c r="B11" s="104" t="s">
-        <x:v>209</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C11" s="102"/>
       <x:c r="D11" s="103" t="s">
-        <x:v>209</x:v>
+        <x:v>178</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -3652,7 +3549,7 @@
       </x:c>
       <x:c r="B12" s="104"/>
       <x:c r="C12" s="51" t="s">
-        <x:v>219</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="D12" s="103"/>
     </x:row>
@@ -3661,62 +3558,62 @@
         <x:v>0.91666666666666663</x:v>
       </x:c>
       <x:c r="B13" s="24" t="s">
-        <x:v>220</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C13" s="48" t="s">
-        <x:v>220</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="D13" s="46" t="s">
-        <x:v>220</x:v>
+        <x:v>189</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="40" t="s">
-        <x:v>221</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="B14" s="57" t="s">
-        <x:v>222</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C14" s="56" t="s">
-        <x:v>222</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="D14" s="43" t="s">
-        <x:v>222</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="15">
       <x:c r="A15" s="47" t="s">
-        <x:v>221</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="B15" s="55" t="s">
-        <x:v>223</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="C15" s="48" t="s">
-        <x:v>223</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="D15" s="45" t="s">
-        <x:v>223</x:v>
+        <x:v>192</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="15"/>
     <x:row r="17" ht="15">
       <x:c r="A17" s="34"/>
       <x:c r="B17" s="35" t="s">
-        <x:v>224</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="C17" s="36" t="s">
-        <x:v>224</x:v>
+        <x:v>193</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="15">
       <x:c r="A18" s="37" t="s">
-        <x:v>205</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="B18" s="39" t="s">
-        <x:v>225</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C18" s="38" t="s">
-        <x:v>226</x:v>
+        <x:v>195</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -3724,10 +3621,10 @@
         <x:v>0.22916666666666666</x:v>
       </x:c>
       <x:c r="B19" s="51" t="s">
-        <x:v>213</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="C19" s="42" t="s">
-        <x:v>210</x:v>
+        <x:v>179</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -3735,10 +3632,10 @@
         <x:v>0.33333333333333331</x:v>
       </x:c>
       <x:c r="B20" s="41" t="s">
-        <x:v>215</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="C20" s="42" t="s">
-        <x:v>215</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -3746,10 +3643,10 @@
         <x:v>0.54166666666666663</x:v>
       </x:c>
       <x:c r="B21" s="51" t="s">
-        <x:v>227</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="C21" s="54" t="s">
-        <x:v>228</x:v>
+        <x:v>197</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -3757,10 +3654,10 @@
         <x:v>0.58333333333333337</x:v>
       </x:c>
       <x:c r="B22" s="41" t="s">
-        <x:v>215</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="C22" s="42" t="s">
-        <x:v>215</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -3768,10 +3665,10 @@
         <x:v>0.79166666666666663</x:v>
       </x:c>
       <x:c r="B23" s="24" t="s">
-        <x:v>229</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="C23" s="103" t="s">
-        <x:v>209</x:v>
+        <x:v>178</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -3779,7 +3676,7 @@
         <x:v>0.83333333333333337</x:v>
       </x:c>
       <x:c r="B24" s="24" t="s">
-        <x:v>216</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C24" s="103"/>
     </x:row>
@@ -3788,30 +3685,30 @@
         <x:v>0.91666666666666663</x:v>
       </x:c>
       <x:c r="B25" s="24" t="s">
-        <x:v>220</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C25" s="46" t="s">
-        <x:v>220</x:v>
+        <x:v>189</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="100" t="s">
-        <x:v>221</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="B26" s="56" t="s">
-        <x:v>222</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C26" s="43" t="s">
-        <x:v>222</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="101"/>
       <x:c r="B27" s="48" t="s">
-        <x:v>223</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="C27" s="45" t="s">
-        <x:v>223</x:v>
+        <x:v>192</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
